--- a/sources/nina_step5b.xlsx
+++ b/sources/nina_step5b.xlsx
@@ -774,6 +774,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
@@ -821,6 +826,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
@@ -866,6 +876,11 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>75937ef0-ab7d-422f-82fa-406485f60d4e</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -8196,6 +8211,11 @@
           <t>Special Tag Throw with Anna only. Anna finishes with a Reverse Shoulder Lock. Total damage is 15,30.</t>
         </is>
       </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
+        </is>
+      </c>
       <c r="Q145" t="inlineStr">
         <is>
           <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
@@ -8233,6 +8253,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
+        </is>
+      </c>
       <c r="Q146" t="inlineStr">
         <is>
           <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
@@ -8275,6 +8300,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
+        </is>
+      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
@@ -8317,6 +8347,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
+        </is>
+      </c>
       <c r="Q148" t="inlineStr">
         <is>
           <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
@@ -8359,6 +8394,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
+        </is>
+      </c>
       <c r="Q149" t="inlineStr">
         <is>
           <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
@@ -8401,6 +8441,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
+        </is>
+      </c>
       <c r="Q150" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
@@ -8443,6 +8488,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
+        </is>
+      </c>
       <c r="Q151" t="inlineStr">
         <is>
           <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
@@ -8485,6 +8535,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
+        </is>
+      </c>
       <c r="Q152" t="inlineStr">
         <is>
           <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
@@ -8532,6 +8587,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
+        </is>
+      </c>
       <c r="Q153" t="inlineStr">
         <is>
           <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
@@ -8574,6 +8634,11 @@
           <t>Initial throw does no damage when doing the Shoulder Buster.</t>
         </is>
       </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
+        </is>
+      </c>
       <c r="Q154" t="inlineStr">
         <is>
           <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
@@ -8616,6 +8681,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
+        </is>
+      </c>
       <c r="Q155" t="inlineStr">
         <is>
           <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
@@ -8668,6 +8738,11 @@
           <t>CH</t>
         </is>
       </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
+        </is>
+      </c>
       <c r="Q156" t="inlineStr">
         <is>
           <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
@@ -8705,6 +8780,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
+        </is>
+      </c>
       <c r="Q157" t="inlineStr">
         <is>
           <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
@@ -8747,6 +8827,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>42ce7230-87bf-452a-b714-833a0716e519</t>
+        </is>
+      </c>
       <c r="Q158" t="inlineStr">
         <is>
           <t>42ce7230-87bf-452a-b714-833a0716e519</t>
@@ -8794,6 +8879,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
+        </is>
+      </c>
       <c r="Q159" t="inlineStr">
         <is>
           <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
@@ -8831,6 +8921,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
+        </is>
+      </c>
       <c r="Q160" t="inlineStr">
         <is>
           <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
@@ -8873,6 +8968,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
+        </is>
+      </c>
       <c r="Q161" t="inlineStr">
         <is>
           <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
@@ -8915,6 +9015,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
+        </is>
+      </c>
       <c r="Q162" t="inlineStr">
         <is>
           <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
@@ -8957,6 +9062,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>f956b41d-482e-44be-a215-575d5455d551</t>
+        </is>
+      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>f956b41d-482e-44be-a215-575d5455d551</t>
@@ -8999,6 +9109,11 @@
           <t>Front</t>
         </is>
       </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>55a9a5db-779c-4431-878f-621fd1035127</t>
+        </is>
+      </c>
       <c r="Q164" t="inlineStr">
         <is>
           <t>55a9a5db-779c-4431-878f-621fd1035127</t>
@@ -9036,6 +9151,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
+        </is>
+      </c>
       <c r="Q165" t="inlineStr">
         <is>
           <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
@@ -9078,6 +9198,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
+        </is>
+      </c>
       <c r="Q166" t="inlineStr">
         <is>
           <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
@@ -9120,6 +9245,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
+        </is>
+      </c>
       <c r="Q167" t="inlineStr">
         <is>
           <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
@@ -9162,6 +9292,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>55349cf9-9743-4042-9932-3196803d0f29</t>
+        </is>
+      </c>
       <c r="Q168" t="inlineStr">
         <is>
           <t>55349cf9-9743-4042-9932-3196803d0f29</t>
@@ -9204,6 +9339,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
+        </is>
+      </c>
       <c r="Q169" t="inlineStr">
         <is>
           <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
@@ -9244,6 +9384,11 @@
       <c r="M170" t="inlineStr">
         <is>
           <t>1+2</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>4d4ecd62-8ffe-41f7-b612-20d6890a6862</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -9388,6 +9533,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
+        </is>
+      </c>
       <c r="Q174" t="inlineStr">
         <is>
           <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
@@ -9420,6 +9570,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
+        </is>
+      </c>
       <c r="Q175" t="inlineStr">
         <is>
           <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
@@ -9452,6 +9607,11 @@
           <t>hhhhhllmlm</t>
         </is>
       </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
+        </is>
+      </c>
       <c r="Q176" t="inlineStr">
         <is>
           <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
@@ -9484,6 +9644,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
+        </is>
+      </c>
       <c r="Q177" t="inlineStr">
         <is>
           <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
@@ -9516,6 +9681,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
+        </is>
+      </c>
       <c r="Q178" t="inlineStr">
         <is>
           <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
@@ -9548,6 +9718,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
+        </is>
+      </c>
       <c r="Q179" t="inlineStr">
         <is>
           <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
@@ -9580,6 +9755,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
+        </is>
+      </c>
       <c r="Q180" t="inlineStr">
         <is>
           <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
@@ -9612,6 +9792,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
+        </is>
+      </c>
       <c r="Q181" t="inlineStr">
         <is>
           <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
@@ -9644,6 +9829,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
+        </is>
+      </c>
       <c r="Q182" t="inlineStr">
         <is>
           <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
@@ -9681,6 +9871,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>f37af239-8d33-4787-93e6-4352245294b9</t>
+        </is>
+      </c>
       <c r="Q183" t="inlineStr">
         <is>
           <t>f37af239-8d33-4787-93e6-4352245294b9</t>
@@ -9718,6 +9913,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
+        </is>
+      </c>
       <c r="Q184" t="inlineStr">
         <is>
           <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
@@ -9753,6 +9953,11 @@
       <c r="K185" t="inlineStr">
         <is>
           <t>hhhhhllmlm</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>d4f56864-b1c5-4ee6-a66e-c349919b767a</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
